--- a/content/B1-محتوا.xlsx
+++ b/content/B1-محتوا.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>موضوع محتوایی</t>
+          <t>ماموریت درس</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>کار و مسئولیت</t>
+          <t>از کار و تجربه مداوم بگو</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>فرایند و سازمان</t>
+          <t>فرایندها را حرفه‌ای توصیف کن</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>سازگاری با تغییر</t>
+          <t>از عادت کردن به تغییر بگو</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>روایت دو لایه</t>
+          <t>دو اتفاق گذشته را مرتب تعریف کن</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>تعریف کردن ماجرا</t>
+          <t>یک داستان شنیدنی تعریف کن</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>تأخیر و برنامه</t>
+          <t>تأخیر و زمان‌بندی را توضیح بده</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>بازگو کردن ماجرا</t>
+          <t>ماجرای دیگران را درست بازگو کن</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>آرزو و فرض</t>
+          <t>اگر دست تو بود چه می‌کردی؟</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>افسوس و آرزو</t>
+          <t>از آرزو و حسرت حرف بزن</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>موقعیت فرضی</t>
+          <t>سناریوهای فرضی را جواب بده</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>شرط و احتیاط</t>
+          <t>شرط بگذار و محتاط حرف بزن</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>حدس درباره گذشته</t>
+          <t>درباره گذشته حدس بزن</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>پشیمانی و انتقاد</t>
+          <t>از پشیمانی و انتقاد بگو</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>تحلیل تصمیم</t>
+          <t>تصمیم‌های گذشته را تحلیل کن</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>مرور تجربه</t>
+          <t>به تجربه‌های گذشته نگاه کن</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>مصاحبه و پرسش</t>
+          <t>مصاحبه و پرسش را گزارش کن</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>گزارش جلسه</t>
+          <t>خلاصه یک جلسه را منتقل کن</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>اختلاف و مذاکره</t>
+          <t>اختلاف و مذاکره را بازگو کن</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>توضیح دوباره</t>
+          <t>یک حرف را ساده‌تر توضیح بده</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>گزارش رسمی</t>
+          <t>رسمی و گزارشی بنویس</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>خبر و شایعه</t>
+          <t>درباره خبر و شایعه حرف بزن</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>خدمات و سفارش کار</t>
+          <t>خدمات بگیر و سفارش کار بده</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>کار روزمره</t>
+          <t>کارهای روزمره را حرفه‌ای‌تر بگو</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>توصیف افراد و جاها</t>
+          <t>آدم‌ها و جاها را دقیق معرفی کن</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>خاطرات</t>
+          <t>از عادت‌های قدیمی و گذشته بگو</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>تضاد و مقایسه</t>
+          <t>تضاد و مقایسه را روشن بیان کن</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>انتخاب و اولویت</t>
+          <t>بین گزینه‌ها بهتر انتخاب کن</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>گفت‌وگوی جدی</t>
+          <t>در بحث جدی نظر بده</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>تصمیم‌گیری</t>
+          <t>دو طرف را بسنج و تصمیم بگیر</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>جمع‌بندی سطح</t>
+          <t>B1 تمام؛ آماده B2</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">

--- a/content/B1-محتوا.xlsx
+++ b/content/B1-محتوا.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ماموریت درس</t>
+          <t>موضوع محتوایی</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>از کار و تجربه مداوم بگو</t>
+          <t>کار و مسئولیت</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>فرایندها را حرفه‌ای توصیف کن</t>
+          <t>فرایند و سازمان</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>از عادت کردن به تغییر بگو</t>
+          <t>سازگاری با تغییر</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>دو اتفاق گذشته را مرتب تعریف کن</t>
+          <t>روایت دو لایه</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>یک داستان شنیدنی تعریف کن</t>
+          <t>تعریف کردن ماجرا</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>تأخیر و زمان‌بندی را توضیح بده</t>
+          <t>تأخیر و برنامه</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ماجرای دیگران را درست بازگو کن</t>
+          <t>بازگو کردن ماجرا</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>اگر دست تو بود چه می‌کردی؟</t>
+          <t>آرزو و فرض</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>از آرزو و حسرت حرف بزن</t>
+          <t>افسوس و آرزو</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>سناریوهای فرضی را جواب بده</t>
+          <t>موقعیت فرضی</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>شرط بگذار و محتاط حرف بزن</t>
+          <t>شرط و احتیاط</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>درباره گذشته حدس بزن</t>
+          <t>حدس درباره گذشته</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>از پشیمانی و انتقاد بگو</t>
+          <t>پشیمانی و انتقاد</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>تصمیم‌های گذشته را تحلیل کن</t>
+          <t>تحلیل تصمیم</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>به تجربه‌های گذشته نگاه کن</t>
+          <t>مرور تجربه</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>مصاحبه و پرسش را گزارش کن</t>
+          <t>مصاحبه و پرسش</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>خلاصه یک جلسه را منتقل کن</t>
+          <t>گزارش جلسه</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>اختلاف و مذاکره را بازگو کن</t>
+          <t>اختلاف و مذاکره</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>یک حرف را ساده‌تر توضیح بده</t>
+          <t>توضیح دوباره</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>رسمی و گزارشی بنویس</t>
+          <t>گزارش رسمی</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>درباره خبر و شایعه حرف بزن</t>
+          <t>خبر و شایعه</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>خدمات بگیر و سفارش کار بده</t>
+          <t>خدمات و سفارش کار</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>کارهای روزمره را حرفه‌ای‌تر بگو</t>
+          <t>کار روزمره</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>آدم‌ها و جاها را دقیق معرفی کن</t>
+          <t>توصیف افراد و جاها</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>از عادت‌های قدیمی و گذشته بگو</t>
+          <t>خاطرات</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>تضاد و مقایسه را روشن بیان کن</t>
+          <t>تضاد و مقایسه</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>بین گزینه‌ها بهتر انتخاب کن</t>
+          <t>انتخاب و اولویت</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>در بحث جدی نظر بده</t>
+          <t>گفت‌وگوی جدی</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>دو طرف را بسنج و تصمیم بگیر</t>
+          <t>تصمیم‌گیری</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>B1 تمام؛ آماده B2</t>
+          <t>جمع‌بندی سطح</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">

--- a/content/B1-محتوا.xlsx
+++ b/content/B1-محتوا.xlsx
@@ -47518,7 +47518,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -47902,7 +47902,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -48286,7 +48286,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -48670,7 +48670,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -49054,7 +49054,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -49438,7 +49438,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -49822,7 +49822,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -50210,7 +50210,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -50598,7 +50598,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -50982,7 +50982,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -51366,7 +51366,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -51754,7 +51754,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -52138,7 +52138,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -52522,7 +52522,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -52906,7 +52906,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -53298,7 +53298,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -53686,7 +53686,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -54070,7 +54070,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -54454,7 +54454,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -54838,7 +54838,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -55222,7 +55222,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -55606,7 +55606,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -55990,7 +55990,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -56374,7 +56374,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -56758,7 +56758,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -57146,7 +57146,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -57534,7 +57534,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -57918,7 +57918,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -58302,7 +58302,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -58686,7 +58686,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
